--- a/report_forms/033_incident_report_tracking--report_forms.xlsx
+++ b/report_forms/033_incident_report_tracking--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Incident Type</t>
+          <t>Incident Type Select</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Incident Severity</t>
+          <t>Incident Severity Select</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Incident Status</t>
+          <t>Incident Status Select</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Incident Status</t>
+          <t>Incident Status Select Options</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
